--- a/public/datos/4.3_Matriz_RACI.xlsx
+++ b/public/datos/4.3_Matriz_RACI.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="RACI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Leyenda" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Enunciado_Caso" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Leyenda_RACI" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Matriz_RACI" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,142 +427,154 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Actividad</t>
+          <t>Sección</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Gerente general</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Coordinadora SIG</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Líderes de proceso</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Auditor interno</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Talento humano</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Colaboradores</t>
+          <t>Detalle del Requerimiento / Parámetros del Caso</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Elaborar documentos del SIG</t>
+          <t>Código de Actividad</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>4.3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aprobar documentos</t>
+          <t>Título del Caso</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Matriz RACI de gobernanza y auditoría de duplicidad de roles</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Controlar el listado maestro</t>
+          <t>Organización</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lácteos del Caribe S.A.S. - Sistema Integrado de Gestión</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Planear auditorías internas</t>
+          <t>1. Situación Problema</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>En la planta ocurrieron incidentes de calidad porque nadie asumió la aprobación del retiro de lotes defectuosos debido a confusión en la asignación de roles.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ejecutar auditorías internas</t>
+          <t>2. Misión del Aprendiz</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Construir la matriz RACI para 8 actividades del SIG, aplicar validación por lista (R;A;C;I), formato condicional de 4 colores y programar fórmula de auditoría de gobernanza.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tratar no conformidades</t>
+          <t>Requerimiento 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Restricción Matricial: Configurar validación de datos en cuadrícula (actividades vs roles) restringida a R; A; C; I.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Realizar la revisión por la dirección</t>
+          <t>Requerimiento 2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Formato Condicional: 4 colores diferenciados: R (Azul), A (Púrpura / Nivel decisorio), C (Ámbar), I (Gris).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Medir indicadores</t>
+          <t>Requerimiento 3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Regla de Gobernanza: Cada actividad debe tener EXACTAMENTE UN Aprobador ('A').</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gestionar riesgos</t>
+          <t>Requerimiento 4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fórmula de Auditoría: En Control Auditoría Gobernanza programar: =SI(CONTAR.SI(B2:G2;'A')=1; 'CONFORME'; SI(CONTAR.SI(B2:G2;'A')=0; 'ERROR: Falta Aprobador'; 'ERROR: Múltiples Aprobadores')).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Capacitar al personal en el SIG</t>
+          <t>Requerimiento 5</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Corrección: Resaltar en rojo los errores y corregir las letras para que todas las actividades queden en estado CONFORME.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Dificultad Clave / Regla Técnica</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>La fórmula lógica horizontal debe contar la letra 'A' en cada fila y diagnosticar con precisión si falta o sobra autoridad aprobatoria.</t>
         </is>
       </c>
     </row>
@@ -581,7 +594,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="54" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -592,12 +605,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Significado</t>
+          <t>Rol RACI</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Qué hace</t>
+          <t>Responsabilidad en el SIG</t>
         </is>
       </c>
     </row>
@@ -614,7 +627,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ejecuta la actividad</t>
+          <t>Ejecuta materialmente la actividad del SIG</t>
         </is>
       </c>
     </row>
@@ -631,7 +644,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Da el visto bueno final y responde por el resultado</t>
+          <t>Autoridad final que aprueba y responde ante auditoría (único por actividad)</t>
         </is>
       </c>
     </row>
@@ -648,7 +661,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aporta su opinión antes de hacerla</t>
+          <t>Experto técnico consultado antes de la toma de decisiones</t>
         </is>
       </c>
     </row>
@@ -665,7 +678,369 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Se le avisa cuando está lista</t>
+          <t>Personal notificado de los resultados de la actividad</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Actividad</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Gerente general</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Coordinadora SIG</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Líderes de proceso</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Auditor interno</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Talento humano</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Colaboradores</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Control Auditoría Gobernanza</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Elaborar documentos del SIG</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aprobar documentos</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Controlar el listado maestro</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Planear auditorías internas</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ejecutar auditorías internas</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tratar no conformidades</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Realizar la revisión por la dirección</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Medir indicadores</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
     </row>
